--- a/static/template_mass.xlsx
+++ b/static/template_mass.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Начисления'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Платежи'!$A$1:$C$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Платежи'!$A$1:$C$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +34,16 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +53,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F6FEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009A6400"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,12 +78,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -441,14 +463,14 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Лицевой счёт</t>
@@ -587,26 +609,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Лицевой счёт</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Дата платежа</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Дата платежа (обязательно)</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Сумма платежа, ₽</t>
         </is>
@@ -620,11 +642,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20.03.2026</t>
+          <t>05.02.2026</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="3">
@@ -635,11 +657,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05.05.2026</t>
+          <t>05.03.2026</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="4">
@@ -650,15 +672,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.04.2026</t>
+          <t>01.03.2026</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ЛС-0002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>01.04.2026</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>500</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C4"/>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -669,72 +706,407 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="115" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Шаблон массового расчёта пеней ЖКУ</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>В листе Начисления одна строка = одно начисление за один период по одному лицевому счёту.</t>
-        </is>
-      </c>
+      <c r="A2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Обязательные поля: Лицевой счёт, Период, Начисление. Срок оплаты можно оставить пустым — он вычислится по правилам 10/15.</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>ЛИСТ «НАЧИСЛЕНИЯ»</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>В листе Платежи одна строка = один поступивший платёж; платежи группируются по лицевому счёту и гасит задолженность FIFO.</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Одна строка = одно начисление за один период по одному лицевому счёту.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Загружайте полные начисления за периоды и историю платежей. Не загружайте итоговый остаток вместе с историей платежей — иначе будет двойное уменьшение.</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Обязательные поля: «Лицевой счёт», «Период», «Начисление, ₽».</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Для каждого ЛС указывайте один вид долга: ЖКУ или капремонт.</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>«Срок оплаты» можно оставить пустым: подставится 10-е число (для сроков до 01.03.2026) или 15-е число (с 01.03.2026) месяца, следующего за расчётным.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Даты допускаются как Excel-даты или текст ДД.ММ.ГГГГ. Суммы — числа, без валютных символов.</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>«Вид долга»: «ЖКУ» или «Капремонт». Для капремонта пени считаются только по 1/300.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Срок оплаты для ЖКУ: до 28.02.2026 включительно — 10-е следующего месяца; начиная с 01.03.2026 — 15-е следующего месяца (ФЗ №177-ФЗ).</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Указывайте ПОЛНОЕ начисление за период, а не текущий остаток долга.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Примеры строк — виртуальные, замените их своими данными.</t>
+      <c r="A9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ЛИСТ «ПЛАТЕЖИ»</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Одна строка = один поступивший платёж.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ОБЯЗАТЕЛЬНО поле «Дата платежа». Без даты расчёт остановится с указанием строки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Платежи распределяются по методу FIFO: сначала гасится самый ранний непогашенный период.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>АВАНСОВЫЕ ПЛАТЕЖИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Аванс — платёж, поступивший РАНЬШЕ срока оплаты того периода, который он закрывает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Если период оплачен полностью до срока, пени по нему не начисляются вообще.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Если авансом закрыта часть суммы, пени идут только на неоплаченный остаток.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Аванс не считается ошибкой: в отчёте он показан отдельной колонкой «в т.ч. авансом».</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Пример: период 01.2026 со сроком 10.02.2026, платёж 05.02.2026 — это аванс.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>ПЕРЕПЛАТА</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Если платежей по лицевому счёту больше, чем начислено, разница — переплата.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Переплата показывается отдельной колонкой и листом «Сверка».</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>По умолчанию расчёт выполняется, а превышение сопровождается предупреждением.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Чтобы запретить такой расчёт, включите на странице расчёта флажок «Строгая проверка: останавливать расчёт при превышении платежей».</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>ВАЖНО: ДВОЙНОЙ ВЫЧЕТ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Нельзя указывать в «Начислениях» остаток долга И одновременно прикладывать платежи: суммы вычтутся дважды.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Признак: сумма платежей заметно больше начислений, а остаток долга в отчёте не сходится.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>При строгой проверке такой реестр будет отклонён с указанием причины.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>АВАНСОВЫЕ ПЛАТЕЖИ И ПЕРЕПЛАТА</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Платёж, внесённый ДО срока оплаты, называется авансом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Аванс закрывает период заранее: пени на закрытую часть не начисляются вовсе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Пример: начислено 4 000 ₽, срок 10.03.2026. Платёж 1 500 ₽ внесён 01.02.2026 (до срока).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Пеня начисляется только на неоплаченные 2 500 ₽, а не на всю сумму.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Если по лицевому счёту оплачено БОЛЬШЕ, чем начислено, разница — переплата.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Переплата показывается отдельно и по периодам не распределяется: пени она не уменьшает,</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  потому что уменьшать уже нечего.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>При загрузке реестра есть выбор:</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  «Разрешить» — авансы и переплата считаются нормальной ситуацией (режим по умолчанию);</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  «Запретить» — расчёт останавливается, если оплачено больше начисленного: удобно</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    при переносе данных, чтобы убедиться, что в «Начислениях» полное начисление,</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    а не остаток долга.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>ЧТО ПОЛУЧИТЕ НА ВЫХОДЕ (6 листов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Сводка — итоги по каждому лицевому счёту, включая аванс и переплату.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Детализация — по периодам: начислено, оплачено, аванс, остаток, дни, пени.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Разбивка — каждый отрезок начисления: база × ставка ÷ доля × дни. Пересчитывается вручную.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Платежи — дата, сумма, тип (аванс / в срок оплаты / с просрочкой) и остаток после зачисления.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Сверка — сопоставление начислений, платежей, аванса и переплаты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Контроль — сверка «итог пеней = сумма отрезков».</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>ГРАНИЦЫ РАСЧЁТА</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Дни 1–30 просрочки — без пеней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Дни 31–90 — 1/300 ставки за каждый день.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>С 91-го дня — 1/130 ставки (для капремонта не применяется).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Срок оплаты: до 28.02.2026 — 10-е число; с 01.03.2026 — 15-е число следующего месяца (ФЗ от 24.06.2025 № 177-ФЗ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Метод ставки выбирается при загрузке. Для долгов до 27.02.2022 разные методы дают разный результат — согласуйте выбор с бухгалтерией и юристом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Примеры строк — виртуальные. Замените их своими данными.</t>
         </is>
       </c>
     </row>
